--- a/output/14_Aviat_Ceragon_기능별_비교.xlsx
+++ b/output/14_Aviat_Ceragon_기능별_비교.xlsx
@@ -16,13 +16,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트비교_요약" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'안내'!$A$1:$B$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'안내'!$A$1:$B$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'품목대응표(1대1)'!$A$1:$E$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'8GHz_2+0_세트비교'!$A$1:$K$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'8GHz_4+0_세트비교'!$A$1:$K$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'11GHz_2+0_세트비교'!$A$1:$K$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'11GHz_4+0_세트비교'!$A$1:$K$14</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'세트비교_요약'!$A$1:$H$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'세트비교_요약'!$A$1:$J$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -488,10 +488,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -534,89 +534,101 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>핵심 구조적 발견 (1) 무선송수신부</t>
+          <t>핵심 구조적 발견 (1) 무선송수신부 - 확인된 사실 vs 추정 구분</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Ceragon RFU-D-HP는 라이선스 설명에 명시된 MC-ABC(멀티캐리어 적응형 대역폭 제어) 기능으로 무선유닛 1대가 반송파 2개를 처리한다 - RFU 총수량이 항상 N/2로 스케일하는 것으로 직접 확인했다(2+0→2, 4+0→4, 6+0→6, 8+0→8, 06번 파일 원본). Aviat는 ODU가 LOW/HIGH 채널별로 분리된 별도 유닛이라 채널 수만큼(N개) 필요하다. 11GHz 2+0에서 Aviat ODU=4(LOW 2+HIGH 2) vs Ceragon RFU=2로 정확히 2배 차이가 나는 것은 이 구조 차이 때문이며 데이터 오류가 아니다.</t>
+          <t>확인된 사실: Ceragon RFU-D-HP 라이선스 설명문에 MC-ABC(멀티캐리어 적응형 대역폭 제어)가 명시돼 있고, RFU 총수량은 항상 N/2로 스케일한다(2+0→2, 4+0→4, 6+0→6, 8+0→8, 06번 파일 원본 수량으로 직접 확인). Aviat는 ODU가 LOW/HIGH 채널별로 분리된 별도 유닛이라 채널 수만큼(N개) 필요한 것도 확인된 사실이다(11GHz 2+0에서 ODU=4 vs RFU=2). 다만 'RFU 1대가 반송파 2개를 내부 처리하기 때문에 이 2배 차이가 생긴다'는 인과 설명 자체는 이 두 사실로부터 도출한 가장 유력한 추정이며, 공급사가 명시적으로 확인해준 내용은 아니다 - 구조 차이로 추정, 기술 확인 필요.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>핵심 구조적 발견 (2) 대역결합기 등장 시점</t>
+          <t>핵심 구조적 발견 (2) 대역결합기 등장 시점 - 확인된 사실 vs 추정 구분</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Ceragon은 RFU 1대가 이미 2채널을 내부 결합하므로 2+0 구성에는 외부 결합기(FXDH 브랜칭 필터)가 BoM에 아예 없고, RFU 2대를 결합해야 하는 4+0부터 등장한다(06번 원본으로 직접 확인). Aviat는 채널마다 별도 ODU이므로 2+0부터 이미 FLAT HYBRID 결합기가 필요하다 - 두 벤더의 '결합기가 필요해지는 시점' 자체가 다른 것이 구조 차이의 또 다른 증거다.</t>
+          <t>확인된 사실: Ceragon 외부 결합기(FXDH 브랜칭 필터)는 2+0 구성 BoM에는 아예 없고, RFU 2대가 쓰이는 4+0부터 등장한다(06번 원본 수량으로 직접 확인). Aviat FLAT HYBRID는 채널별 ODU 구조상 2+0부터 이미 필요하다는 것도 확인된 사실이다. '두 벤더의 결합기 등장 시점이 다른 이유가 RFU의 반송파 내부결합 때문'이라는 설명은 유력한 추정이나, 공급사 기술 확인 전까지는 추정 단계로 취급한다.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>핵심 구조적 발견 (3) 섀시 용량</t>
+          <t>수량 환산 근거(왜 관측수량을 그대로 링크 전체 수량으로 보는가)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Ceragon IP-20N-1RU/5-Slot IDU는 슬롯 여유가 있어 2+0/4+0 모두 사이트당 섀시 1대로 커버된다(수량 고정 확인). Aviat VR4 1RU CHASSIS는 (참고 후보 수준이라 확정은 아니지만) 8GHz 4+0 관측에서 사이트당 2대로 늘어나는 패턴이 나타나 - 다만 11GHz 4+0 관측에서는 사이트당 1대로 나타나 두 참고 후보 관측이 서로 불일치한다. 이 항목은 패턴 확정이 아니라 공급사 확인이 필요한 항목으로 남긴다.</t>
+          <t>Aviat 발주이력에는 Ceragon처럼 'A국소/B국소' 구분이 없어, 관측된 원 수량을 사이트당으로 볼지 링크 전체로 볼지가 그 자체로는 불확실하다. 이 표는 Ceragon의 명시적 관례(1개링크_A국소수량 + B국소수량 = 총수량, 즉 두 끝 사이트 합산이 링크 총량)를 기준으로 삼아 Aviat 원 관측수량을 '링크 전체 수량'으로 그대로 두었다 (즉 배수×N=원 관측수량이 되도록 정의). 근거는 추정이 아니라 교차검증이다 - 11GHz 2+0에서 Aviat가 실제로 주문한 원 수량(Chassis/License/Fan/Mount 4개 품목 모두 2)이 Ceragon이 공식 제출한 링크 총수량(같은 4개 품목 모두 2)과 정확히 일치한다 - 만약 Aviat의 '2'가 사이트당 수량이었다면 링크 전체는 4가 되어야 하므로 Ceragon과 어긋났을 것이다. 다만 이 관례를 Aviat가 명시적으로 확인해준 것은 아니므로 공급사 확인 항목으로 남겨둔다(07번 파일 공급사확인사항 참조).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>수량 이상치 제외 기준</t>
+          <t>핵심 구조적 발견 (3) 섀시 용량</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Aviat 참고 후보 품목 중 '구성비 배수'(N당 배수)가 6을 넘는 품목은 세트비교 카테고리 합계에서 제외했다 - 이런 품목은 대부분 VR10 계열(대용량 집중국/허브 장비)이 VR4/해당 대역 신호와 같은 발주 이벤트 창에 우연히 함께 있었던 것으로 보이며(예: 11GHz 2+0 관측 창에 VR10 Node License 14개·FAN-MV 28개 등이 섞여 있음), 1개 링크 단위로 억지로 환산하면 오히려 왜곡된 비교가 된다. 제외된 품목은 각 세트비교 시트의 '제외 품목' 열에 그대로 남겨 투명하게 표시했다(임의로 숨기지 않음).</t>
+          <t>Ceragon IP-20N-1RU/5-Slot IDU는 슬롯 여유가 있어 2+0/4+0 모두 사이트당 섀시 1대로 커버된다(수량 고정 확인). Aviat VR4 1RU CHASSIS는 (참고 후보 수준이라 확정은 아니지만) 8GHz 4+0 관측에서 사이트당 2대로 늘어나는 패턴이 나타나 - 다만 11GHz 4+0 관측에서는 사이트당 1대로 나타나 두 참고 후보 관측이 서로 불일치한다. 이 항목은 패턴 확정이 아니라 공급사 확인이 필요한 항목으로 남긴다.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>제외한 품목군</t>
+          <t>수량 이상치 제외 기준</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>케이블·커넥터·안테나·접지·방수자재 등은 이번 기능대응표에서 다루지 않았다(각 세트비교 시트 맨 아래 '기타' 행에 건수·금액만 합산). 이런 품목은 현장 시공 조건(케이블 길이, 철탑 형태 등)에 따라 달라져 코드나 설명만으로 1:1 대응을 주장하기 어렵기 때문이다 - 강제로 매칭하면 이 프로젝트가 처음부터 지켜온 '문자열 유사도만으로 동일 품목 단정 금지' 원칙에 어긋난다.</t>
+          <t>Aviat 참고 후보 품목 중 '구성비 배수'(N당 배수)가 6을 넘는 품목은 세트비교 카테고리 합계에서 제외했다 - 이런 품목은 대부분 VR10 계열(대용량 집중국/허브 장비)이 VR4/해당 대역 신호와 같은 발주 이벤트 창에 우연히 함께 있었던 것으로 보이며(예: 11GHz 2+0 관측 창에 VR10 Node License 14개·FAN-MV 28개 등이 섞여 있음), 1개 링크 단위로 억지로 환산하면 오히려 왜곡된 비교가 된다. 제외된 품목은 각 세트비교 시트의 '제외 품목' 열에 그대로 남겨 투명하게 표시했다(임의로 숨기지 않음).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>가장 근거가 뚜렷한 세트</t>
+          <t>제외한 품목군</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>11GHz 2+0만 유력 후보(독립 2개 이벤트로 반복 확인) 품목이 있다 - 본체/무선송수신부/팬/라이선스/마운트 5개 카테고리, 6개 품목, 실제 수량 기준 참고 판매총액 19,088,472원. 나머지 3개 구성(8GHz 2+0/4+0, 11GHz 4+0)은 전 카테고리가 참고 후보(단일 관측)뿐이라 세트비교표는 있지만 신뢰도가 그만큼 낮다.</t>
+          <t>케이블·커넥터·안테나·접지·방수자재 등은 이번 기능대응표에서 다루지 않았다(각 세트비교 시트 맨 아래 '기타' 행에 건수·금액만 합산). 이런 품목은 현장 시공 조건(케이블 길이, 철탑 형태 등)에 따라 달라져 코드나 설명만으로 1:1 대응을 주장하기 어렵기 때문이다 - 강제로 매칭하면 이 프로젝트가 처음부터 지켜온 '문자열 유사도만으로 동일 품목 단정 금지' 원칙에 어긋난다.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>읽는 법</t>
+          <t>가장 근거가 뚜렷한 세트 - 그러나 아직 직접 비교는 불가</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>각 '세트비교' 시트는 11개 기능분류를 행으로 하고, Aviat 유력후보/참고후보(신뢰도 분리)와 Ceragon Non_SD/SD 금액을 나란히 놓았다. 맨 아래 '소계'는 케이블 등 기타를 제외한 핵심 11개 카테고리만의 합계로, 처음으로 두 공급사를 거의 같은 범위에서 비교할 수 있는 숫자다. 다만 이마저도 Aviat 쪽이 참고 후보(단일 관측) 품목을 포함하면 신뢰도가 낮아지므로, 최종 협상 근거는 반드시 애니콤 정식 회신으로 교체해야 한다.</t>
+          <t>11GHz 2+0만 유력 후보(독립 2개 이벤트로 반복 확인) 품목이 있다 - 본체/무선송수신부/팬/라이선스/마운트 5개 카테고리, 6개 품목, 실제 수량 기준 참고 판매총액 19,088,472원. 그러나 이 5개 카테고리는 11개 핵심 카테고리 중 일부일 뿐이다 - 대역결합기·인터페이스카드·제어카드·전원·SFP는 11GHz 2+0에서도 참고 후보(단일 관측)로만 존재하거나 아예 근거가 없다. 즉 Aviat 유력후보 19,088,472원을 Ceragon 핵심11종 합계(35~47백만원)와 곧바로 비교하면 서로 다른 범위를 비교하는 것이다 - 나머지 3개 구성(8GHz 2+0/4+0, 11GHz 4+0)은 전 카테고리가 참고 후보뿐이라 신뢰도가 더 낮다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>읽는 법 및 현재 활용 범위</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>각 '세트비교' 시트는 11개 기능분류를 행으로 하고, Aviat 유력후보/참고후보(신뢰도 분리)와 Ceragon Non_SD/SD 금액을 나란히 놓았다. 맨 아래 '소계'는 케이블 등 기타를 제외한 핵심 11개 카테고리만의 합계로 비교 '범위'를 맞추려는 시도이지만, Aviat 유력후보만으로는 이 11개 카테고리를 다 채우지 못한다(위 항목 참조) - 정확히 말하면 '비교 틀은 마련됐으나 유력후보 기준 직접 가격비교는 아직 불가'다. 참고후보까지 합쳐야 11개 카테고리가 채워지지만, 참고후보는 단일 관측이라 신뢰도가 낮다. 지금 이 파일의 안전한 활용 범위는 (1)품목 대응구조 설명 (2)대성 BoM 누락 품목 점검 (3)애니콤 확인 질문 작성이며, 세트 금액을 가격 확정·인하 요구의 근거로 쓰는 것은 아직 이르다 - 반드시 애니콤 정식 회신으로 유력후보 범위를 넓힌 뒤 다시 봐야 한다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B10"/>
+  <autoFilter ref="A1:B11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1162,7 +1174,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>둘 다 라디오/인터페이스/제어카드를 수납하는 본체 셀프. Ceragon 설명: '1RU, 5+0까지 구성 가능한 IDU 셀프' - 슬롯 여유가 있어 2+0/4+0 모두 섀시 1대(사이트당)로 커버되는 것이 정상.</t>
+          <t>둘 다 라디오/인터페이스/제어카드를 수납하는 본체 셀프. Ceragon 설명: '1RU, 5+0까지 구성 가능한 IDU 셀프' - 슬롯 여유가 있어 2+0/4+0 모두 섀시 1대(사이트당)로 커버되는 것으로 추정(공급사 확인 필요).</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1213,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Ceragon RFU-D-HP는 라이선스에 포함된 MC-ABC(멀티캐리어 적응형 대역폭 제어) 기능으로 무선유닛 1대가 반송파(채널) 2개를 처리한다(RFU 총수량이 항상 N/2로 스케일: 2+0→2, 4+0→4 확인됨). Aviat는 ODU가 LOW/HIGH 채널별로 별도 유닛이라 채널 수만큼 필요 - 그 결과 Aviat 수량이 Ceragon의 2배로 나오는 것은 구조 차이이며 오류가 아니다.</t>
+          <t>사실로 확인되는 것: Ceragon 설명문에 MC-ABC(멀티캐리어 적응형 대역폭 제어)가 명시돼 있고, RFU 총수량은 항상 N/2로 스케일한다(2+0→2, 4+0→4, 06번 원본 수량 직접 확인). Aviat는 ODU가 LOW/HIGH 채널별 별도 유닛이라 채널 수만큼(N개) 필요하다는 것도 확인된 사실이다. 다만 '이 두 사실이 결합해 무선유닛 1대가 반송파 2개를 처리하기 때문에 수량이 2배 차이난다'는 인과관계 자체는 설명문·수량 패턴에서 나온 가장 유력한 추정이며, 공급사가 직접 확인해준 것은 아니다 - 구조 차이로 추정, 기술 확인 필요.</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1246,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Ceragon 설명 '채널필터 브랜칭' - Aviat FLAT HYBRID와 동일하게 서로 다른 채널을 하나의 안테나로 결합/분리하는 수동소자. Ceragon은 RFU 1대가 이미 내부에서 2채널을 결합하므로 2+0에서는 이 부품 자체가 BoM에 없고, RFU 2대를 묶어야 하는 4+0부터 등장한다(확인됨). Aviat는 채널마다 별도 ODU라 2+0부터 이미 결합기가 필요 - 두 벤더의 '등장 시점'이 다른 것 자체가 구조 차이의 증거.</t>
+          <t>사실로 확인되는 것: Ceragon 설명문 '채널필터 브랜칭'(Aviat FLAT HYBRID와 같은 대역결합/분리 수동소자 역할)과, 이 부품이 2+0 구성 BoM에는 없고 4+0부터 등장한다는 수량 패턴(06번 원본 확인)이다. Aviat는 채널별 별도 ODU 구조라 2+0부터 이미 결합기가 필요하다. '두 벤더의 결합기 등장 시점이 다른 이유가 RFU의 반송파 내부결합 때문'이라는 설명은 유력한 추정이나, 공급사 기술 확인 전까지는 추정 단계로 취급한다.</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1736,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>둘 다 라디오/인터페이스/제어카드를 수납하는 본체 셀프. Ceragon 설명: '1RU, 5+0까지 구성 가능한 IDU 셀프' - 슬롯 여유가 있어 2+0/4+0 모두 섀시 1대(사이트당)로 커버되는 것이 정상.</t>
+          <t>둘 다 라디오/인터페이스/제어카드를 수납하는 본체 셀프. Ceragon 설명: '1RU, 5+0까지 구성 가능한 IDU 셀프' - 슬롯 여유가 있어 2+0/4+0 모두 섀시 1대(사이트당)로 커버되는 것으로 추정(공급사 확인 필요).</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1775,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Ceragon RFU-D-HP는 라이선스에 포함된 MC-ABC(멀티캐리어 적응형 대역폭 제어) 기능으로 무선유닛 1대가 반송파(채널) 2개를 처리한다(RFU 총수량이 항상 N/2로 스케일: 2+0→2, 4+0→4 확인됨). Aviat는 ODU가 LOW/HIGH 채널별로 별도 유닛이라 채널 수만큼 필요 - 그 결과 Aviat 수량이 Ceragon의 2배로 나오는 것은 구조 차이이며 오류가 아니다.</t>
+          <t>사실로 확인되는 것: Ceragon 설명문에 MC-ABC(멀티캐리어 적응형 대역폭 제어)가 명시돼 있고, RFU 총수량은 항상 N/2로 스케일한다(2+0→2, 4+0→4, 06번 원본 수량 직접 확인). Aviat는 ODU가 LOW/HIGH 채널별 별도 유닛이라 채널 수만큼(N개) 필요하다는 것도 확인된 사실이다. 다만 '이 두 사실이 결합해 무선유닛 1대가 반송파 2개를 처리하기 때문에 수량이 2배 차이난다'는 인과관계 자체는 설명문·수량 패턴에서 나온 가장 유력한 추정이며, 공급사가 직접 확인해준 것은 아니다 - 구조 차이로 추정, 기술 확인 필요.</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1814,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Ceragon 설명 '채널필터 브랜칭' - Aviat FLAT HYBRID와 동일하게 서로 다른 채널을 하나의 안테나로 결합/분리하는 수동소자. Ceragon은 RFU 1대가 이미 내부에서 2채널을 결합하므로 2+0에서는 이 부품 자체가 BoM에 없고, RFU 2대를 묶어야 하는 4+0부터 등장한다(확인됨). Aviat는 채널마다 별도 ODU라 2+0부터 이미 결합기가 필요 - 두 벤더의 '등장 시점'이 다른 것 자체가 구조 차이의 증거.</t>
+          <t>사실로 확인되는 것: Ceragon 설명문 '채널필터 브랜칭'(Aviat FLAT HYBRID와 같은 대역결합/분리 수동소자 역할)과, 이 부품이 2+0 구성 BoM에는 없고 4+0부터 등장한다는 수량 패턴(06번 원본 확인)이다. Aviat는 채널별 별도 ODU 구조라 2+0부터 이미 결합기가 필요하다. '두 벤더의 결합기 등장 시점이 다른 이유가 RFU의 반송파 내부결합 때문'이라는 설명은 유력한 추정이나, 공급사 기술 확인 전까지는 추정 단계로 취급한다.</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2302,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>둘 다 라디오/인터페이스/제어카드를 수납하는 본체 셀프. Ceragon 설명: '1RU, 5+0까지 구성 가능한 IDU 셀프' - 슬롯 여유가 있어 2+0/4+0 모두 섀시 1대(사이트당)로 커버되는 것이 정상.</t>
+          <t>둘 다 라디오/인터페이스/제어카드를 수납하는 본체 셀프. Ceragon 설명: '1RU, 5+0까지 구성 가능한 IDU 셀프' - 슬롯 여유가 있어 2+0/4+0 모두 섀시 1대(사이트당)로 커버되는 것으로 추정(공급사 확인 필요).</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2341,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Ceragon RFU-D-HP는 라이선스에 포함된 MC-ABC(멀티캐리어 적응형 대역폭 제어) 기능으로 무선유닛 1대가 반송파(채널) 2개를 처리한다(RFU 총수량이 항상 N/2로 스케일: 2+0→2, 4+0→4 확인됨). Aviat는 ODU가 LOW/HIGH 채널별로 별도 유닛이라 채널 수만큼 필요 - 그 결과 Aviat 수량이 Ceragon의 2배로 나오는 것은 구조 차이이며 오류가 아니다.</t>
+          <t>사실로 확인되는 것: Ceragon 설명문에 MC-ABC(멀티캐리어 적응형 대역폭 제어)가 명시돼 있고, RFU 총수량은 항상 N/2로 스케일한다(2+0→2, 4+0→4, 06번 원본 수량 직접 확인). Aviat는 ODU가 LOW/HIGH 채널별 별도 유닛이라 채널 수만큼(N개) 필요하다는 것도 확인된 사실이다. 다만 '이 두 사실이 결합해 무선유닛 1대가 반송파 2개를 처리하기 때문에 수량이 2배 차이난다'는 인과관계 자체는 설명문·수량 패턴에서 나온 가장 유력한 추정이며, 공급사가 직접 확인해준 것은 아니다 - 구조 차이로 추정, 기술 확인 필요.</t>
         </is>
       </c>
     </row>
@@ -2360,7 +2372,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Ceragon 설명 '채널필터 브랜칭' - Aviat FLAT HYBRID와 동일하게 서로 다른 채널을 하나의 안테나로 결합/분리하는 수동소자. Ceragon은 RFU 1대가 이미 내부에서 2채널을 결합하므로 2+0에서는 이 부품 자체가 BoM에 없고, RFU 2대를 묶어야 하는 4+0부터 등장한다(확인됨). Aviat는 채널마다 별도 ODU라 2+0부터 이미 결합기가 필요 - 두 벤더의 '등장 시점'이 다른 것 자체가 구조 차이의 증거.</t>
+          <t>사실로 확인되는 것: Ceragon 설명문 '채널필터 브랜칭'(Aviat FLAT HYBRID와 같은 대역결합/분리 수동소자 역할)과, 이 부품이 2+0 구성 BoM에는 없고 4+0부터 등장한다는 수량 패턴(06번 원본 확인)이다. Aviat는 채널별 별도 ODU 구조라 2+0부터 이미 결합기가 필요하다. '두 벤더의 결합기 등장 시점이 다른 이유가 RFU의 반송파 내부결합 때문'이라는 설명은 유력한 추정이나, 공급사 기술 확인 전까지는 추정 단계로 취급한다.</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2894,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>둘 다 라디오/인터페이스/제어카드를 수납하는 본체 셀프. Ceragon 설명: '1RU, 5+0까지 구성 가능한 IDU 셀프' - 슬롯 여유가 있어 2+0/4+0 모두 섀시 1대(사이트당)로 커버되는 것이 정상.</t>
+          <t>둘 다 라디오/인터페이스/제어카드를 수납하는 본체 셀프. Ceragon 설명: '1RU, 5+0까지 구성 가능한 IDU 셀프' - 슬롯 여유가 있어 2+0/4+0 모두 섀시 1대(사이트당)로 커버되는 것으로 추정(공급사 확인 필요).</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2933,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Ceragon RFU-D-HP는 라이선스에 포함된 MC-ABC(멀티캐리어 적응형 대역폭 제어) 기능으로 무선유닛 1대가 반송파(채널) 2개를 처리한다(RFU 총수량이 항상 N/2로 스케일: 2+0→2, 4+0→4 확인됨). Aviat는 ODU가 LOW/HIGH 채널별로 별도 유닛이라 채널 수만큼 필요 - 그 결과 Aviat 수량이 Ceragon의 2배로 나오는 것은 구조 차이이며 오류가 아니다.</t>
+          <t>사실로 확인되는 것: Ceragon 설명문에 MC-ABC(멀티캐리어 적응형 대역폭 제어)가 명시돼 있고, RFU 총수량은 항상 N/2로 스케일한다(2+0→2, 4+0→4, 06번 원본 수량 직접 확인). Aviat는 ODU가 LOW/HIGH 채널별 별도 유닛이라 채널 수만큼(N개) 필요하다는 것도 확인된 사실이다. 다만 '이 두 사실이 결합해 무선유닛 1대가 반송파 2개를 처리하기 때문에 수량이 2배 차이난다'는 인과관계 자체는 설명문·수량 패턴에서 나온 가장 유력한 추정이며, 공급사가 직접 확인해준 것은 아니다 - 구조 차이로 추정, 기술 확인 필요.</t>
         </is>
       </c>
     </row>
@@ -2960,7 +2972,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Ceragon 설명 '채널필터 브랜칭' - Aviat FLAT HYBRID와 동일하게 서로 다른 채널을 하나의 안테나로 결합/분리하는 수동소자. Ceragon은 RFU 1대가 이미 내부에서 2채널을 결합하므로 2+0에서는 이 부품 자체가 BoM에 없고, RFU 2대를 묶어야 하는 4+0부터 등장한다(확인됨). Aviat는 채널마다 별도 ODU라 2+0부터 이미 결합기가 필요 - 두 벤더의 '등장 시점'이 다른 것 자체가 구조 차이의 증거.</t>
+          <t>사실로 확인되는 것: Ceragon 설명문 '채널필터 브랜칭'(Aviat FLAT HYBRID와 같은 대역결합/분리 수동소자 역할)과, 이 부품이 2+0 구성 BoM에는 없고 4+0부터 등장한다는 수량 패턴(06번 원본 확인)이다. Aviat는 채널별 별도 ODU 구조라 2+0부터 이미 결합기가 필요하다. '두 벤더의 결합기 등장 시점이 다른 이유가 RFU의 반송파 내부결합 때문'이라는 설명은 유력한 추정이나, 공급사 기술 확인 전까지는 추정 단계로 취급한다.</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3348,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="27" customWidth="1" min="6" max="6"/>
-    <col width="23" customWidth="1" min="7" max="7"/>
-    <col width="70" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="27" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="70" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -3357,35 +3371,45 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Aviat 유력후보 합계(핵심11종)</t>
+          <t>Aviat 유력후보 카테고리 수(11개 중)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Aviat 유력후보 합계(해당 카테고리만)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Aviat 참고후보 합계(안정, 핵심11종)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Ceragon(Non_SD) 핵심11종 합계</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Ceragon(SD) 핵심11종 합계</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Ceragon(Non_SD) 전체 총액(참고)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Ceragon(SD) 전체 총액(참고)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>직접 가격비교 가능 여부</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
@@ -3397,25 +3421,35 @@
           <t>8GHz 2+0</t>
         </is>
       </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>0/11</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="n"/>
+      <c r="D2" s="3" t="n">
         <v>32808288</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>35356545.59</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>47432792.34</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="G2" s="3" t="n">
         <v>35608005.346</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="H2" s="3" t="n">
         <v>47710885.87800001</v>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>전 카테고리가 참고 후보(단일 관측)뿐 - 세트 합계도 참고용일 뿐 협상 근거로 쓰지 않는다.</t>
+      <c r="I2" s="6" t="inlineStr">
+        <is>
+          <t>불가(카테고리 범위 다름)</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>전 카테고리가 참고 후보(단일 관측)뿐이거나 근거가 없다 - 세트 합계도 참고용일 뿐 협상 근거로 쓰지 않는다.</t>
         </is>
       </c>
     </row>
@@ -3425,25 +3459,35 @@
           <t>8GHz 4+0</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>0/11</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="n"/>
+      <c r="D3" s="3" t="n">
         <v>47007556</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>55426376.53999999</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>65593357.738</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="G3" s="3" t="n">
         <v>55704470.07799999</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="H3" s="3" t="n">
         <v>65924718.84</v>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>전 카테고리가 참고 후보(단일 관측)뿐 - 세트 합계도 참고용일 뿐 협상 근거로 쓰지 않는다.</t>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>불가(카테고리 범위 다름)</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>전 카테고리가 참고 후보(단일 관측)뿐이거나 근거가 없다 - 세트 합계도 참고용일 뿐 협상 근거로 쓰지 않는다.</t>
         </is>
       </c>
     </row>
@@ -3453,27 +3497,37 @@
           <t>11GHz 2+0</t>
         </is>
       </c>
-      <c r="B4" s="7" t="n">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>5/11</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="n">
         <v>19088472</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>26625786</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>35356545.59</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>47431698.104</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="G4" s="3" t="n">
         <v>35608005.346</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="H4" s="3" t="n">
         <v>47709791.642</v>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>가장 근거가 뚜렷한 구성 - 유력후보 합계는 독립 2개 이벤트로 반복 확인된 6개 품목 기준. '핵심11종' 열끼리는 범위가 거의 같아 처음으로 apples-to-apples에 가까운 비교가 가능하다(단, Aviat 참고후보 포함분은 여전히 단일 관측이라 신뢰도가 낮음).</t>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>불가(카테고리 범위 다름)</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>유력후보는 11개 카테고리 중 5개(① 본체/섀시(IDU·Chassis), ② 무선송수신부(ODU/RFU), ⑥ 라이선스/설정SW, ⑦ 냉각팬, ⑨ 마운팅/브래킷)만 채운다 - 대역결합기·인터페이스카드·제어카드·전원·SFP는 유력후보가 없어 Ceragon 핵심11종 합계와 범위가 다르다. 따라서 19,088,472원을 35~47백만원과 직접 비교하면 서로 다른 범위를 비교하는 것이다 - '비교 틀은 마련됐으나 유력후보만으로는 아직 직접 가격비교 불가'가 정확한 표현이다. 참고후보까지 합치면 11개 카테고리가 채워지지만 참고후보는 단일 관측이라 신뢰도가 낮다.</t>
         </is>
       </c>
     </row>
@@ -3483,30 +3537,40 @@
           <t>11GHz 4+0</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n">
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>0/11</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n">
         <v>40129488</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>55424188.068</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>65591169.266</v>
       </c>
-      <c r="F5" s="3" t="n">
+      <c r="G5" s="3" t="n">
         <v>55702281.606</v>
       </c>
-      <c r="G5" s="3" t="n">
+      <c r="H5" s="3" t="n">
         <v>65922530.36799999</v>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>전 카테고리가 참고 후보(단일 관측)뿐 - 세트 합계도 참고용일 뿐 협상 근거로 쓰지 않는다.</t>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>불가(카테고리 범위 다름)</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>전 카테고리가 참고 후보(단일 관측)뿐이거나 근거가 없다 - 세트 합계도 참고용일 뿐 협상 근거로 쓰지 않는다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H5"/>
+  <autoFilter ref="A1:J5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/14_Aviat_Ceragon_기능별_비교.xlsx
+++ b/output/14_Aviat_Ceragon_기능별_비교.xlsx
@@ -558,12 +558,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>수량 환산 근거(왜 관측수량을 그대로 링크 전체 수량으로 보는가)</t>
+          <t>수량 환산 가정(왜 관측수량을 링크 전체 수량으로 해석하는가 - 확정 아님)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Aviat 발주이력에는 Ceragon처럼 'A국소/B국소' 구분이 없어, 관측된 원 수량을 사이트당으로 볼지 링크 전체로 볼지가 그 자체로는 불확실하다. 이 표는 Ceragon의 명시적 관례(1개링크_A국소수량 + B국소수량 = 총수량, 즉 두 끝 사이트 합산이 링크 총량)를 기준으로 삼아 Aviat 원 관측수량을 '링크 전체 수량'으로 그대로 두었다 (즉 배수×N=원 관측수량이 되도록 정의). 근거는 추정이 아니라 교차검증이다 - 11GHz 2+0에서 Aviat가 실제로 주문한 원 수량(Chassis/License/Fan/Mount 4개 품목 모두 2)이 Ceragon이 공식 제출한 링크 총수량(같은 4개 품목 모두 2)과 정확히 일치한다 - 만약 Aviat의 '2'가 사이트당 수량이었다면 링크 전체는 4가 되어야 하므로 Ceragon과 어긋났을 것이다. 다만 이 관례를 Aviat가 명시적으로 확인해준 것은 아니므로 공급사 확인 항목으로 남겨둔다(07번 파일 공급사확인사항 참조).</t>
+          <t>확인되는 사실은 하나뿐이다: 11GHz 2+0에서 Chassis/License/Fan/Mount 4개 품목 모두 Aviat 발주이력상 원 관측수량이 2였고, Ceragon이 공식 제출한 같은 기능군의 링크 총수량도 4개 품목 모두 2였다(수치 일치). 이 표는 Ceragon의 명시적 관례(A국소+B국소=총수량, 두 끝 사이트 합산이 링크 총량)를 Aviat 원 관측수량에도 적용해 '링크 전체 수량'으로 해석한다(배수×N=원 관측수량이 되도록 정의). 그러나 이 수치 일치는 해석을 뒷받침하는 정황 증거일 뿐, Aviat 수량 정의 자체를 증명하지 않는다 - Aviat의 '2'가 우연히 같았을 수도 있고, 한 발주에 링크 2개분이 포함됐을 가능성도 원칙적으로 배제되지 않는다. 따라서 19,088,472원은 '발주이력에서 핵심 품목이 각각 2개로 관측됐고, 이를 링크 전체 수량으로 해석하면 나오는 값'이며, Ceragon 수량과 정합하지만 Aviat 공식 BoM 확인 전까지는 확정이 아니라 '링크 환산 가정'으로 표시한다(07번 파일 공급사확인사항에 이 가정 자체를 확인 질문으로 포함).</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>11GHz 2+0만 유력 후보(독립 2개 이벤트로 반복 확인) 품목이 있다 - 본체/무선송수신부/팬/라이선스/마운트 5개 카테고리, 6개 품목, 실제 수량 기준 참고 판매총액 19,088,472원. 그러나 이 5개 카테고리는 11개 핵심 카테고리 중 일부일 뿐이다 - 대역결합기·인터페이스카드·제어카드·전원·SFP는 11GHz 2+0에서도 참고 후보(단일 관측)로만 존재하거나 아예 근거가 없다. 즉 Aviat 유력후보 19,088,472원을 Ceragon 핵심11종 합계(35~47백만원)와 곧바로 비교하면 서로 다른 범위를 비교하는 것이다 - 나머지 3개 구성(8GHz 2+0/4+0, 11GHz 4+0)은 전 카테고리가 참고 후보뿐이라 신뢰도가 더 낮다.</t>
+          <t>11GHz 2+0만 유력 후보(독립 2개 이벤트로 반복 확인) 품목이 있다 - 본체/무선송수신부/팬/라이선스/마운트 5개 카테고리, 6개 품목, 링크 환산 가정 기준 참고 판매총액 19,088,472원(위 '수량 환산 가정' 항목 참조 - 확정 아님). 그러나 이 5개 카테고리는 11개 핵심 카테고리 중 일부일 뿐이다 - 대역결합기·인터페이스카드·제어카드·전원·SFP는 11GHz 2+0에서도 참고 후보(단일 관측)로만 존재하거나 아예 근거가 없다. 즉 Aviat 유력후보 19,088,472원을 Ceragon 핵심11종 합계(35~47백만원)와 곧바로 비교하면 서로 다른 범위를 비교하는 것이다 - 나머지 3개 구성(8GHz 2+0/4+0, 11GHz 4+0)은 전 카테고리가 참고 후보뿐이라 신뢰도가 더 낮다.</t>
         </is>
       </c>
     </row>
@@ -3353,8 +3353,8 @@
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="27" customWidth="1" min="7" max="7"/>
@@ -3376,12 +3376,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Aviat 유력후보 합계(해당 카테고리만)</t>
+          <t>Aviat 유력후보 합계(해당 카테고리만, 링크 환산 가정)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Aviat 참고후보 합계(안정, 핵심11종)</t>
+          <t>Aviat 참고후보 합계(안정, 핵심11종, 링크 환산 가정)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">

--- a/output/14_Aviat_Ceragon_기능별_비교.xlsx
+++ b/output/14_Aviat_Ceragon_기능별_비교.xlsx
@@ -16,7 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트비교_요약" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'안내'!$A$1:$B$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'안내'!$A$1:$B$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'품목대응표(1대1)'!$A$1:$E$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'8GHz_2+0_세트비교'!$A$1:$K$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'8GHz_4+0_세트비교'!$A$1:$K$14</definedName>
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -534,101 +534,113 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>핵심 구조적 발견 (1) 무선송수신부 - 확인된 사실 vs 추정 구분</t>
+          <t>가장 중요한 한 문장(2026-09-08, 3차 검토에서 합의)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>확인된 사실: Ceragon RFU-D-HP 라이선스 설명문에 MC-ABC(멀티캐리어 적응형 대역폭 제어)가 명시돼 있고, RFU 총수량은 항상 N/2로 스케일한다(2+0→2, 4+0→4, 6+0→6, 8+0→8, 06번 파일 원본 수량으로 직접 확인). Aviat는 ODU가 LOW/HIGH 채널별로 분리된 별도 유닛이라 채널 수만큼(N개) 필요한 것도 확인된 사실이다(11GHz 2+0에서 ODU=4 vs RFU=2). 다만 'RFU 1대가 반송파 2개를 내부 처리하기 때문에 이 2배 차이가 생긴다'는 인과 설명 자체는 이 두 사실로부터 도출한 가장 유력한 추정이며, 공급사가 명시적으로 확인해준 내용은 아니다 - 구조 차이로 추정, 기술 확인 필요.</t>
+          <t>11GHz 2+0 유력후보 19,088,472원(링크 환산 가정, 내부 참고값)이 Ceragon 핵심11종 합계(35~47백만원)보다 작게 나오는 것은 'Aviat가 더 싸다'는 뜻이 아니라 'Aviat 유력후보가 아직 완성 BoM 금액이 아니다'라는 뜻이다 - 11개 핵심 기능군 중 본체/무선송수신부/팬/라이선스/마운트 5개만 채워져 있고, 대역결합기·인터페이스카드·제어카드·전원·SFP는 유력후보 근거가 없다. 지금 단계에서 방어 가능한 실무 결론은 '대성 가격이 비싸다/싸다'가 아니라 '같은 범위로 비교할 근거가 아직 부족하다'이다.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>핵심 구조적 발견 (2) 대역결합기 등장 시점 - 확인된 사실 vs 추정 구분</t>
+          <t>핵심 구조적 발견 (1) 무선송수신부 - 확인된 사실 vs 추정 구분</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>확인된 사실: Ceragon 외부 결합기(FXDH 브랜칭 필터)는 2+0 구성 BoM에는 아예 없고, RFU 2대가 쓰이는 4+0부터 등장한다(06번 원본 수량으로 직접 확인). Aviat FLAT HYBRID는 채널별 ODU 구조상 2+0부터 이미 필요하다는 것도 확인된 사실이다. '두 벤더의 결합기 등장 시점이 다른 이유가 RFU의 반송파 내부결합 때문'이라는 설명은 유력한 추정이나, 공급사 기술 확인 전까지는 추정 단계로 취급한다.</t>
+          <t>확인된 사실: Ceragon RFU-D-HP 라이선스 설명문에 MC-ABC(멀티캐리어 적응형 대역폭 제어)가 명시돼 있고, RFU 총수량은 항상 N/2로 스케일한다(2+0→2, 4+0→4, 6+0→6, 8+0→8, 06번 파일 원본 수량으로 직접 확인). Aviat는 ODU가 LOW/HIGH 채널별로 분리된 별도 유닛이라 채널 수만큼(N개) 필요한 것도 확인된 사실이다(11GHz 2+0에서 ODU=4 vs RFU=2). 다만 'RFU 1대가 반송파 2개를 내부 처리하기 때문에 이 2배 차이가 생긴다'는 인과 설명 자체는 이 두 사실로부터 도출한 가장 유력한 추정이며, 공급사가 명시적으로 확인해준 내용은 아니다 - 구조 차이로 추정, 기술 확인 필요.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>수량 환산 가정(왜 관측수량을 링크 전체 수량으로 해석하는가 - 확정 아님)</t>
+          <t>핵심 구조적 발견 (2) 대역결합기 등장 시점 - 확인된 사실 vs 추정 구분</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>확인되는 사실은 하나뿐이다: 11GHz 2+0에서 Chassis/License/Fan/Mount 4개 품목 모두 Aviat 발주이력상 원 관측수량이 2였고, Ceragon이 공식 제출한 같은 기능군의 링크 총수량도 4개 품목 모두 2였다(수치 일치). 이 표는 Ceragon의 명시적 관례(A국소+B국소=총수량, 두 끝 사이트 합산이 링크 총량)를 Aviat 원 관측수량에도 적용해 '링크 전체 수량'으로 해석한다(배수×N=원 관측수량이 되도록 정의). 그러나 이 수치 일치는 해석을 뒷받침하는 정황 증거일 뿐, Aviat 수량 정의 자체를 증명하지 않는다 - Aviat의 '2'가 우연히 같았을 수도 있고, 한 발주에 링크 2개분이 포함됐을 가능성도 원칙적으로 배제되지 않는다. 따라서 19,088,472원은 '발주이력에서 핵심 품목이 각각 2개로 관측됐고, 이를 링크 전체 수량으로 해석하면 나오는 값'이며, Ceragon 수량과 정합하지만 Aviat 공식 BoM 확인 전까지는 확정이 아니라 '링크 환산 가정'으로 표시한다(07번 파일 공급사확인사항에 이 가정 자체를 확인 질문으로 포함).</t>
+          <t>확인된 사실: Ceragon 외부 결합기(FXDH 브랜칭 필터)는 2+0 구성 BoM에는 아예 없고, RFU 2대가 쓰이는 4+0부터 등장한다(06번 원본 수량으로 직접 확인). Aviat FLAT HYBRID는 채널별 ODU 구조상 2+0부터 이미 필요하다는 것도 확인된 사실이다. '두 벤더의 결합기 등장 시점이 다른 이유가 RFU의 반송파 내부결합 때문'이라는 설명은 유력한 추정이나, 공급사 기술 확인 전까지는 추정 단계로 취급한다.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>핵심 구조적 발견 (3) 섀시 용량</t>
+          <t>수량 환산 가정(왜 관측수량을 링크 전체 수량으로 해석하는가 - 확정 아님)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Ceragon IP-20N-1RU/5-Slot IDU는 슬롯 여유가 있어 2+0/4+0 모두 사이트당 섀시 1대로 커버된다(수량 고정 확인). Aviat VR4 1RU CHASSIS는 (참고 후보 수준이라 확정은 아니지만) 8GHz 4+0 관측에서 사이트당 2대로 늘어나는 패턴이 나타나 - 다만 11GHz 4+0 관측에서는 사이트당 1대로 나타나 두 참고 후보 관측이 서로 불일치한다. 이 항목은 패턴 확정이 아니라 공급사 확인이 필요한 항목으로 남긴다.</t>
+          <t>확인되는 사실은 하나뿐이다: 11GHz 2+0에서 Chassis/License/Fan/Mount 4개 품목 모두 Aviat 발주이력상 원 관측수량이 2였고, Ceragon이 공식 제출한 같은 기능군의 링크 총수량도 4개 품목 모두 2였다(수치 일치). 이 표는 Ceragon의 명시적 관례(A국소+B국소=총수량, 두 끝 사이트 합산이 링크 총량)를 Aviat 원 관측수량에도 적용해 '링크 전체 수량'으로 해석한다(배수×N=원 관측수량이 되도록 정의). 그러나 이 수치 일치는 해석을 뒷받침하는 정황 증거일 뿐, Aviat 수량 정의 자체를 증명하지 않는다 - Aviat의 '2'가 우연히 같았을 수도 있고, 한 발주에 링크 2개분이 포함됐을 가능성도 원칙적으로 배제되지 않는다. 따라서 19,088,472원은 '발주이력에서 핵심 품목이 각각 2개로 관측됐고, 이를 링크 전체 수량으로 해석하면 나오는 값'이며, Ceragon 수량과 정합하지만 Aviat 공식 BoM 확인 전까지는 확정이 아니라 '링크 환산 가정'으로 표시한다(07번 파일 공급사확인사항에 이 가정 자체를 확인 질문으로 포함).</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>수량 이상치 제외 기준</t>
+          <t>핵심 구조적 발견 (3) 섀시 용량</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Aviat 참고 후보 품목 중 '구성비 배수'(N당 배수)가 6을 넘는 품목은 세트비교 카테고리 합계에서 제외했다 - 이런 품목은 대부분 VR10 계열(대용량 집중국/허브 장비)이 VR4/해당 대역 신호와 같은 발주 이벤트 창에 우연히 함께 있었던 것으로 보이며(예: 11GHz 2+0 관측 창에 VR10 Node License 14개·FAN-MV 28개 등이 섞여 있음), 1개 링크 단위로 억지로 환산하면 오히려 왜곡된 비교가 된다. 제외된 품목은 각 세트비교 시트의 '제외 품목' 열에 그대로 남겨 투명하게 표시했다(임의로 숨기지 않음).</t>
+          <t>Ceragon IP-20N-1RU/5-Slot IDU는 슬롯 여유가 있어 2+0/4+0 모두 사이트당 섀시 1대로 커버된다(수량 고정 확인). Aviat VR4 1RU CHASSIS는 (참고 후보 수준이라 확정은 아니지만) 8GHz 4+0 관측에서 사이트당 2대로 늘어나는 패턴이 나타나 - 다만 11GHz 4+0 관측에서는 사이트당 1대로 나타나 두 참고 후보 관측이 서로 불일치한다. 이 항목은 패턴 확정이 아니라 공급사 확인이 필요한 항목으로 남긴다.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>제외한 품목군</t>
+          <t>수량 이상치 제외 기준</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>케이블·커넥터·안테나·접지·방수자재 등은 이번 기능대응표에서 다루지 않았다(각 세트비교 시트 맨 아래 '기타' 행에 건수·금액만 합산). 이런 품목은 현장 시공 조건(케이블 길이, 철탑 형태 등)에 따라 달라져 코드나 설명만으로 1:1 대응을 주장하기 어렵기 때문이다 - 강제로 매칭하면 이 프로젝트가 처음부터 지켜온 '문자열 유사도만으로 동일 품목 단정 금지' 원칙에 어긋난다.</t>
+          <t>Aviat 참고 후보 품목 중 '구성비 배수'(N당 배수)가 6을 넘는 품목은 세트비교 카테고리 합계에서 제외했다 - 이런 품목은 대부분 VR10 계열(대용량 집중국/허브 장비)이 VR4/해당 대역 신호와 같은 발주 이벤트 창에 우연히 함께 있었던 것으로 보이며(예: 11GHz 2+0 관측 창에 VR10 Node License 14개·FAN-MV 28개 등이 섞여 있음), 1개 링크 단위로 억지로 환산하면 오히려 왜곡된 비교가 된다. 제외된 품목은 각 세트비교 시트의 '제외 품목' 열에 그대로 남겨 투명하게 표시했다(임의로 숨기지 않음).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>가장 근거가 뚜렷한 세트 - 그러나 아직 직접 비교는 불가</t>
+          <t>제외한 품목군</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>11GHz 2+0만 유력 후보(독립 2개 이벤트로 반복 확인) 품목이 있다 - 본체/무선송수신부/팬/라이선스/마운트 5개 카테고리, 6개 품목, 링크 환산 가정 기준 참고 판매총액 19,088,472원(위 '수량 환산 가정' 항목 참조 - 확정 아님). 그러나 이 5개 카테고리는 11개 핵심 카테고리 중 일부일 뿐이다 - 대역결합기·인터페이스카드·제어카드·전원·SFP는 11GHz 2+0에서도 참고 후보(단일 관측)로만 존재하거나 아예 근거가 없다. 즉 Aviat 유력후보 19,088,472원을 Ceragon 핵심11종 합계(35~47백만원)와 곧바로 비교하면 서로 다른 범위를 비교하는 것이다 - 나머지 3개 구성(8GHz 2+0/4+0, 11GHz 4+0)은 전 카테고리가 참고 후보뿐이라 신뢰도가 더 낮다.</t>
+          <t>케이블·커넥터·안테나·접지·방수자재 등은 이번 기능대응표에서 다루지 않았다(각 세트비교 시트 맨 아래 '기타' 행에 건수·금액만 합산). 이런 품목은 현장 시공 조건(케이블 길이, 철탑 형태 등)에 따라 달라져 코드나 설명만으로 1:1 대응을 주장하기 어렵기 때문이다 - 강제로 매칭하면 이 프로젝트가 처음부터 지켜온 '문자열 유사도만으로 동일 품목 단정 금지' 원칙에 어긋난다.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>가장 근거가 뚜렷한 세트 - 그러나 아직 직접 비교는 불가</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>11GHz 2+0만 유력 후보(독립 2개 이벤트로 반복 확인) 품목이 있다 - 본체/무선송수신부/팬/라이선스/마운트 5개 카테고리, 6개 품목, 링크 환산 가정 기준 참고 판매총액 19,088,472원(위 '수량 환산 가정' 항목 참조 - 확정 아님). 그러나 이 5개 카테고리는 11개 핵심 카테고리 중 일부일 뿐이다 - 대역결합기·인터페이스카드·제어카드·전원·SFP는 11GHz 2+0에서도 참고 후보(단일 관측)로만 존재하거나 아예 근거가 없다. 즉 Aviat 유력후보 19,088,472원을 Ceragon 핵심11종 합계(35~47백만원)와 곧바로 비교하면 서로 다른 범위를 비교하는 것이다 - 나머지 3개 구성(8GHz 2+0/4+0, 11GHz 4+0)은 전 카테고리가 참고 후보뿐이라 신뢰도가 더 낮다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>읽는 법 및 현재 활용 범위</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>각 '세트비교' 시트는 11개 기능분류를 행으로 하고, Aviat 유력후보/참고후보(신뢰도 분리)와 Ceragon Non_SD/SD 금액을 나란히 놓았다. 맨 아래 '소계'는 케이블 등 기타를 제외한 핵심 11개 카테고리만의 합계로 비교 '범위'를 맞추려는 시도이지만, Aviat 유력후보만으로는 이 11개 카테고리를 다 채우지 못한다(위 항목 참조) - 정확히 말하면 '비교 틀은 마련됐으나 유력후보 기준 직접 가격비교는 아직 불가'다. 참고후보까지 합쳐야 11개 카테고리가 채워지지만, 참고후보는 단일 관측이라 신뢰도가 낮다. 지금 이 파일의 안전한 활용 범위는 (1)품목 대응구조 설명 (2)대성 BoM 누락 품목 점검 (3)애니콤 확인 질문 작성이며, 세트 금액을 가격 확정·인하 요구의 근거로 쓰는 것은 아직 이르다 - 반드시 애니콤 정식 회신으로 유력후보 범위를 넓힌 뒤 다시 봐야 한다.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B11"/>
+  <autoFilter ref="A1:B12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
